--- a/sample-data/qTaxonomy.xlsx
+++ b/sample-data/qTaxonomy.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,6 +486,11 @@
           <t>Execution Strategy</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>P-card Policy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -553,6 +558,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -620,6 +630,11 @@
           <t>Catalogue</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -687,6 +702,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -754,6 +774,11 @@
           <t>Catalogue</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -821,6 +846,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -888,6 +918,11 @@
           <t>Catalogue</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -955,6 +990,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1022,6 +1062,11 @@
           <t>Catalogue</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1089,6 +1134,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1156,6 +1206,11 @@
           <t>Catalogue</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1223,6 +1278,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1290,6 +1350,11 @@
           <t>Catalogue</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1357,6 +1422,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1424,6 +1494,11 @@
           <t>Catalogue</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1491,6 +1566,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1558,6 +1638,11 @@
           <t>Catalogue</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1625,6 +1710,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1692,6 +1782,11 @@
           <t>Catalogue</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1759,6 +1854,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1826,6 +1926,11 @@
           <t>Catalogue</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1893,6 +1998,11 @@
           <t>Contract</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1958,6 +2068,11 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>Catalogue</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Restricted</t>
         </is>
       </c>
     </row>

--- a/sample-data/qTaxonomy.xlsx
+++ b/sample-data/qTaxonomy.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2076,6 +2076,798 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>F23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Facilities Management</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C023</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Workwear</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CM0023</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Workwear</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Protective Workwear</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Synthetic description for workwear</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Procurement Led</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Centre-led</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>F24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Transport, Logistics, Warehousing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C024</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Courier &amp; Postal</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CM0024</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Courier</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Courier Services</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Synthetic description for courier</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Procurement Led</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Centre-led</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>F25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Facilities Management</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C025</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Hygiene</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CM0025</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pest control</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pest Control Services</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Synthetic description for pest control</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Procurement Led</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Centre-led</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>F26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sales, Communication &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>C026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Digital Marketing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CM0026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Digital analytics</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Digital Analytics Services</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Synthetic description for digital analytics</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Business Led</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>F27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C027</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Language Services</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CM0027</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Translation Services</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Synthetic description for translation</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Procurement Led</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Centre-led</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>F28</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C028</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Strategy Advisory</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CM0028</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Strategy advisory</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Corporate Strategy Advisory</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Synthetic description for strategy advisory</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Business Led</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>F29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sales, Communication &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C029</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Trade Investment</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CM0029</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rebates</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Customer Rebates</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Synthetic description for rebates</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Business Led</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>F30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>C030</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CM0030</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Office Rent</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Synthetic description for rent</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Business Led</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Research &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C031</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Lab Supplies</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CM0031</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lab supplies</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Laboratory Supplies</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Synthetic description for lab supplies</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Procurement Led</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Centre-led</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Research &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>C032</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CM0032</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lab Testing</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Lab Testing - Microbiology</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Synthetic description for lab testing</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Business Led</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Indirect</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>F33</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Research &amp; Quality</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>C033</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CM0033</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lab Testing</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Lab Testing - Chemistry</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Synthetic description for lab testing</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Business Led</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Tactical</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
